--- a/Design-Files/OFP_SCM_v1.5/BOM/Client-BOM-OFP_SCM_v1.5.xlsx
+++ b/Design-Files/OFP_SCM_v1.5/BOM/Client-BOM-OFP_SCM_v1.5.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="168">
   <si>
     <t>#</t>
   </si>
@@ -288,9 +288,6 @@
     <t>X9555WV-2x12-6TV01</t>
   </si>
   <si>
-    <t>ETQP3M6R8KVN</t>
-  </si>
-  <si>
     <t>LED-0603</t>
   </si>
   <si>
@@ -441,9 +438,6 @@
     <t>YLPTEC</t>
   </si>
   <si>
-    <t>Comment</t>
-  </si>
-  <si>
     <t>10uF</t>
   </si>
   <si>
@@ -468,12 +462,6 @@
     <t>6.8uH</t>
   </si>
   <si>
-    <t>Blue</t>
-  </si>
-  <si>
-    <t>RED</t>
-  </si>
-  <si>
     <t>10K</t>
   </si>
   <si>
@@ -510,14 +498,38 @@
     <t>Quantity</t>
   </si>
   <si>
-    <t>#Column Name Error:' Remarks</t>
+    <t>Peripheral</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dupont wire / terminal block wire / electronic wire </t>
+  </si>
+  <si>
+    <t>Custom</t>
+  </si>
+  <si>
+    <t>XF-P00014</t>
+  </si>
+  <si>
+    <t>XFCN</t>
+  </si>
+  <si>
+    <t>We can also ask custom supplier on this as the actual cable length that is required is 150mm. The above parts have 300mm wire length. We can ask to find part number of B8B-XH-A (LF)(SN) connector or XH series 8 pin connector with 150mm length.</t>
+  </si>
+  <si>
+    <t>value</t>
+  </si>
+  <si>
+    <t>Remarks</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -556,6 +568,14 @@
     <font>
       <b/>
       <sz val="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -676,7 +696,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -715,6 +735,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1003,18 +1026,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K35"/>
+  <dimension ref="A1:K36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3.140625" style="4" customWidth="1"/>
     <col min="3" max="3" width="18.7109375" style="4" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="36" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="30" customWidth="1"/>
-    <col min="6" max="6" width="26.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="33.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.7109375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="29.42578125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1049,19 +1072,19 @@
         <v>81</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>140</v>
+        <v>166</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1083,13 +1106,13 @@
         <v>82</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="J3" s="7">
         <v>10</v>
@@ -1099,7 +1122,7 @@
     <row r="4" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
       <c r="B4" s="11">
-        <f t="shared" ref="B4:B35" si="0">ROW(B4) - ROW($B$2)</f>
+        <f t="shared" ref="B4:B34" si="0">ROW(B4) - ROW($B$2)</f>
         <v>2</v>
       </c>
       <c r="C4" s="13" t="s">
@@ -1115,13 +1138,13 @@
         <v>82</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="J4" s="9">
         <v>21</v>
@@ -1147,13 +1170,13 @@
         <v>82</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="J5" s="7">
         <v>1</v>
@@ -1179,13 +1202,13 @@
         <v>83</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="J6" s="9">
         <v>2</v>
@@ -1211,13 +1234,13 @@
         <v>84</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="J7" s="7">
         <v>2</v>
@@ -1243,13 +1266,13 @@
         <v>82</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="J8" s="9">
         <v>1</v>
@@ -1275,13 +1298,13 @@
         <v>83</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="J9" s="7">
         <v>1</v>
@@ -1307,13 +1330,13 @@
         <v>82</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="J10" s="9">
         <v>1</v>
@@ -1336,16 +1359,16 @@
         <v>57</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>85</v>
+        <v>162</v>
       </c>
       <c r="G11" s="8" t="s">
         <v>85</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>85</v>
+        <v>160</v>
       </c>
       <c r="J11" s="7">
         <v>1</v>
@@ -1371,13 +1394,13 @@
         <v>86</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="I12" s="10" t="s">
-        <v>107</v>
+        <v>129</v>
+      </c>
+      <c r="I12" s="8" t="s">
+        <v>160</v>
       </c>
       <c r="J12" s="9">
         <v>1</v>
@@ -1400,16 +1423,16 @@
         <v>59</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>87</v>
+        <v>162</v>
       </c>
       <c r="G13" s="8" t="s">
         <v>87</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>87</v>
+        <v>160</v>
       </c>
       <c r="J13" s="7">
         <v>1</v>
@@ -1431,17 +1454,17 @@
       <c r="E14" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="F14" s="9" t="s">
-        <v>88</v>
+      <c r="F14" s="7" t="s">
+        <v>162</v>
       </c>
       <c r="G14" s="10" t="s">
         <v>88</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>132</v>
-      </c>
-      <c r="I14" s="10" t="s">
-        <v>88</v>
+        <v>131</v>
+      </c>
+      <c r="I14" s="8" t="s">
+        <v>160</v>
       </c>
       <c r="J14" s="9">
         <v>5</v>
@@ -1464,16 +1487,16 @@
         <v>61</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>89</v>
+        <v>162</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="J15" s="7">
         <v>1</v>
@@ -1496,16 +1519,16 @@
         <v>62</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="J16" s="9">
         <v>4</v>
@@ -1528,16 +1551,16 @@
         <v>63</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="I17" s="8" t="s">
-        <v>150</v>
+        <v>133</v>
+      </c>
+      <c r="I17" s="10" t="s">
+        <v>160</v>
       </c>
       <c r="J17" s="7">
         <v>1</v>
@@ -1560,16 +1583,16 @@
         <v>64</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="J18" s="9">
         <v>1</v>
@@ -1592,16 +1615,16 @@
         <v>65</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="J19" s="7">
         <v>3</v>
@@ -1624,16 +1647,16 @@
         <v>66</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="J20" s="9">
         <v>7</v>
@@ -1656,16 +1679,16 @@
         <v>67</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I21" s="8" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="J21" s="7">
         <v>5</v>
@@ -1688,16 +1711,16 @@
         <v>68</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="J22" s="9">
         <v>3</v>
@@ -1720,16 +1743,16 @@
         <v>69</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="J23" s="7">
         <v>1</v>
@@ -1752,16 +1775,16 @@
         <v>70</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G24" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="J24" s="9">
         <v>1</v>
@@ -1784,16 +1807,16 @@
         <v>71</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I25" s="8" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="J25" s="7">
         <v>1</v>
@@ -1816,16 +1839,16 @@
         <v>72</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G26" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I26" s="10" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="J26" s="9">
         <v>1</v>
@@ -1848,16 +1871,16 @@
         <v>73</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I27" s="8" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="J27" s="7">
         <v>1</v>
@@ -1880,16 +1903,16 @@
         <v>74</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G28" s="10" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H28" s="9" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I28" s="10" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="J28" s="9">
         <v>1</v>
@@ -1912,16 +1935,16 @@
         <v>75</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>92</v>
+        <v>162</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H29" s="7" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I29" s="8" t="s">
-        <v>92</v>
+        <v>160</v>
       </c>
       <c r="J29" s="7">
         <v>2</v>
@@ -1944,16 +1967,16 @@
         <v>76</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G30" s="10" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H30" s="9" t="s">
-        <v>136</v>
-      </c>
-      <c r="I30" s="10" t="s">
-        <v>122</v>
+        <v>135</v>
+      </c>
+      <c r="I30" s="8" t="s">
+        <v>160</v>
       </c>
       <c r="J30" s="9">
         <v>1</v>
@@ -1976,16 +1999,16 @@
         <v>77</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G31" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H31" s="7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I31" s="8" t="s">
-        <v>123</v>
+        <v>160</v>
       </c>
       <c r="J31" s="7">
         <v>1</v>
@@ -2008,16 +2031,16 @@
         <v>78</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G32" s="10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H32" s="9" t="s">
-        <v>138</v>
-      </c>
-      <c r="I32" s="10" t="s">
-        <v>124</v>
+        <v>137</v>
+      </c>
+      <c r="I32" s="8" t="s">
+        <v>160</v>
       </c>
       <c r="J32" s="9">
         <v>1</v>
@@ -2040,16 +2063,16 @@
         <v>79</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H33" s="7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I33" s="8" t="s">
-        <v>125</v>
+        <v>160</v>
       </c>
       <c r="J33" s="7">
         <v>1</v>
@@ -2071,17 +2094,17 @@
       <c r="E34" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="F34" s="9" t="s">
-        <v>97</v>
+      <c r="F34" s="7" t="s">
+        <v>162</v>
       </c>
       <c r="G34" s="10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H34" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="I34" s="10" t="s">
-        <v>97</v>
+        <v>138</v>
+      </c>
+      <c r="I34" s="8" t="s">
+        <v>160</v>
       </c>
       <c r="J34" s="9">
         <v>1</v>
@@ -2104,21 +2127,54 @@
         <v>79</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H35" s="7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I35" s="8" t="s">
-        <v>126</v>
+        <v>160</v>
       </c>
       <c r="J35" s="7">
         <v>3</v>
       </c>
       <c r="K35" s="7"/>
+    </row>
+    <row r="36" spans="1:11" ht="102.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B36" s="11">
+        <f>ROW(B36) - ROW($B$2)</f>
+        <v>34</v>
+      </c>
+      <c r="C36" s="12" t="s">
+        <v>159</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="E36" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="F36" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="G36" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="H36" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="I36" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="J36" s="7">
+        <v>1</v>
+      </c>
+      <c r="K36" s="15" t="s">
+        <v>165</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
